--- a/datasets/prompt_dataset.xlsx
+++ b/datasets/prompt_dataset.xlsx
@@ -10,7 +10,7 @@
     <sheet name="prompt_dataset" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'prompt_dataset'!$A$1:$E$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'prompt_dataset'!$A$1:$E$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,14 +436,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1823,8 +1823,278 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>P051</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Read the text from samples/ocr/receipt_01.png.</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>OCR Extraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>P052</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Extract the item names and prices from samples/ocr/menu_01.png.</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>OCR Extraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>P053</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>What date is shown in samples/ocr/invoice_01.png?</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>OCR Extraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>P054</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Transcribe the handwritten note in samples/ocr/note_01.png exactly.</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>OCR Transcription</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>P055</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Extract all visible text from the noisy sign in samples/ocr/sign_01.png.</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>OCR Extraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>P056</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Image Understanding</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Describe the main object shown in samples/ocr/photo_01.png.</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Visual Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>P057</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Image Understanding</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Count how many people are visible in samples/ocr/classroom_01.png.</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Visual Counting</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>P058</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Image Understanding</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>What is the likely setting shown in samples/ocr/street_01.png?</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Scene Understanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>P059</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Image Understanding</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Identify any visible safety issues in samples/ocr/worksite_01.png.</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Visual Risk Detection</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>P060</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Image Understanding</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Describe the color and layout details in samples/ocr/chart_01.png.</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Visual Description</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E51"/>
+  <autoFilter ref="A1:E61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>